--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/bu-04/HRM/post DFS_HRM-2031-0192/Panel-28/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/bu-04/HRM/post DFS_HRM-2031-0192/Panel-28/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.18648</v>
+        <v>17.10147</v>
       </c>
       <c r="D2" t="n">
-        <v>16.77045</v>
+        <v>16.69784</v>
       </c>
       <c r="E2" t="n">
-        <v>16.83558</v>
+        <v>16.88142</v>
       </c>
       <c r="F2" t="n">
-        <v>43.09587</v>
+        <v>42.57534</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05076</v>
+        <v>0.05199</v>
       </c>
       <c r="H2" t="n">
-        <v>1.86863</v>
+        <v>1.85427</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.97183</v>
+        <v>17.1837</v>
       </c>
       <c r="D3" t="n">
-        <v>16.90245</v>
+        <v>16.56621</v>
       </c>
       <c r="E3" t="n">
-        <v>16.81067</v>
+        <v>16.57412</v>
       </c>
       <c r="F3" t="n">
-        <v>42.62212</v>
+        <v>43.47324</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05196</v>
+        <v>0.05183</v>
       </c>
       <c r="H3" t="n">
-        <v>1.82802</v>
+        <v>1.8547</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.32692</v>
+        <v>17.04517</v>
       </c>
       <c r="D4" t="n">
-        <v>16.42772</v>
+        <v>16.67514</v>
       </c>
       <c r="E4" t="n">
-        <v>16.77906</v>
+        <v>16.99229</v>
       </c>
       <c r="F4" t="n">
-        <v>42.6325</v>
+        <v>42.58096</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05129</v>
+        <v>0.05095</v>
       </c>
       <c r="H4" t="n">
-        <v>1.85726</v>
+        <v>1.87771</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.26222</v>
+        <v>16.71639</v>
       </c>
       <c r="D6" t="n">
-        <v>15.88495</v>
+        <v>16.23432</v>
       </c>
       <c r="E6" t="n">
-        <v>16.60534</v>
+        <v>16.29804</v>
       </c>
       <c r="F6" t="n">
-        <v>21.99603</v>
+        <v>22.04665</v>
       </c>
       <c r="G6" t="n">
-        <v>34.61363</v>
+        <v>34.3597</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.75205</v>
+        <v>16.89094</v>
       </c>
       <c r="D7" t="n">
-        <v>15.90965</v>
+        <v>16.31858</v>
       </c>
       <c r="E7" t="n">
-        <v>16.55896</v>
+        <v>16.37995</v>
       </c>
       <c r="F7" t="n">
-        <v>21.807</v>
+        <v>21.62378</v>
       </c>
       <c r="G7" t="n">
-        <v>35.00847</v>
+        <v>34.29094</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.79985</v>
+        <v>16.99474</v>
       </c>
       <c r="D8" t="n">
-        <v>16.1488</v>
+        <v>15.98063</v>
       </c>
       <c r="E8" t="n">
-        <v>16.97644</v>
+        <v>16.91754</v>
       </c>
       <c r="F8" t="n">
-        <v>22.58452</v>
+        <v>22.26292</v>
       </c>
       <c r="G8" t="n">
-        <v>34.0769</v>
+        <v>34.65525</v>
       </c>
     </row>
   </sheetData>
